--- a/TableauSynthese/CPL_TableauDeSynthese.xlsx
+++ b/TableauSynthese/CPL_TableauDeSynthese.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="45">
   <si>
     <t xml:space="preserve">BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">NOM et prénom :   Place Clément</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
+    <t xml:space="preserve">N°  Candidat : 02047453398</t>
   </si>
   <si>
     <t xml:space="preserve">Centre de formation : Campus La Chataigneraie</t>
@@ -52,27 +52,7 @@
     <t xml:space="preserve">X SLAM</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Adresse URL du portfolio : </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://apollofr76.github.io/Portfolio/</t>
-    </r>
+    <t xml:space="preserve">Adresse URL du portfolio : https://apollofr76.github.io/Portfolio/</t>
   </si>
   <si>
     <t xml:space="preserve">Compétences mises en œuvre
@@ -193,6 +173,9 @@
   </si>
   <si>
     <t xml:space="preserve">Application MAUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Symfony (Erasmus)</t>
   </si>
 </sst>
 </file>
@@ -334,56 +317,56 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -710,17 +693,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" s="5" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -757,29 +740,29 @@
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2"/>
     </row>
-    <row r="6" s="4" customFormat="true" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" s="5" customFormat="true" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="2"/>
@@ -818,537 +801,722 @@
       <c r="AP6" s="2"/>
       <c r="AQ6" s="2"/>
     </row>
-    <row r="7" s="4" customFormat="true" ht="324.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="8" t="s">
+    <row r="7" s="5" customFormat="true" ht="324.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="true" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+    <row r="8" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+    </row>
+    <row r="9" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="11"/>
+    </row>
+    <row r="21" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="11"/>
+    </row>
+    <row r="22" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9" t="s">
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-    </row>
-    <row r="26" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-    </row>
-    <row r="27" s="4" customFormat="true" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-    </row>
-    <row r="28" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-    </row>
-    <row r="29" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-    </row>
-    <row r="30" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" s="4" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" s="5" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10" t="s">
-        <v>26</v>
-      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+      <c r="AA27" s="5"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="5"/>
+      <c r="AF27" s="5"/>
+      <c r="AG27" s="5"/>
+      <c r="AH27" s="5"/>
+      <c r="AI27" s="5"/>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="5"/>
+      <c r="AL27" s="5"/>
+      <c r="AM27" s="5"/>
+      <c r="AN27" s="5"/>
+      <c r="AO27" s="5"/>
+      <c r="AP27" s="5"/>
+      <c r="AQ27" s="5"/>
+    </row>
+    <row r="28" s="2" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="10"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="5"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="5"/>
+      <c r="AD28" s="5"/>
+      <c r="AE28" s="5"/>
+      <c r="AF28" s="5"/>
+      <c r="AG28" s="5"/>
+      <c r="AH28" s="5"/>
+      <c r="AI28" s="5"/>
+      <c r="AJ28" s="5"/>
+      <c r="AK28" s="5"/>
+      <c r="AL28" s="5"/>
+      <c r="AM28" s="5"/>
+      <c r="AN28" s="5"/>
+      <c r="AO28" s="5"/>
+      <c r="AP28" s="5"/>
+      <c r="AQ28" s="5"/>
+    </row>
+    <row r="29" s="2" customFormat="true" ht="51.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="5"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="5"/>
+      <c r="AD29" s="5"/>
+      <c r="AE29" s="5"/>
+      <c r="AF29" s="5"/>
+      <c r="AG29" s="5"/>
+      <c r="AH29" s="5"/>
+      <c r="AI29" s="5"/>
+      <c r="AJ29" s="5"/>
+      <c r="AK29" s="5"/>
+      <c r="AL29" s="5"/>
+      <c r="AM29" s="5"/>
+      <c r="AN29" s="5"/>
+      <c r="AO29" s="5"/>
+      <c r="AP29" s="5"/>
+      <c r="AQ29" s="5"/>
+    </row>
+    <row r="30" s="2" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
+      <c r="C30" s="0"/>
+      <c r="D30" s="0"/>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0"/>
+      <c r="G30" s="0"/>
+      <c r="H30" s="0"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+      <c r="AA30" s="5"/>
+      <c r="AB30" s="5"/>
+      <c r="AC30" s="5"/>
+      <c r="AD30" s="5"/>
+      <c r="AE30" s="5"/>
+      <c r="AF30" s="5"/>
+      <c r="AG30" s="5"/>
+      <c r="AH30" s="5"/>
+      <c r="AI30" s="5"/>
+      <c r="AJ30" s="5"/>
+      <c r="AK30" s="5"/>
+      <c r="AL30" s="5"/>
+      <c r="AM30" s="5"/>
+      <c r="AN30" s="5"/>
+      <c r="AO30" s="5"/>
+      <c r="AP30" s="5"/>
+      <c r="AQ30" s="5"/>
+    </row>
+    <row r="31" s="2" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
+      <c r="C31" s="0"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0"/>
+      <c r="G31" s="0"/>
+      <c r="H31" s="0"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+      <c r="AA31" s="5"/>
+      <c r="AB31" s="5"/>
+      <c r="AC31" s="5"/>
+      <c r="AD31" s="5"/>
+      <c r="AE31" s="5"/>
+      <c r="AF31" s="5"/>
+      <c r="AG31" s="5"/>
+      <c r="AH31" s="5"/>
+      <c r="AI31" s="5"/>
+      <c r="AJ31" s="5"/>
+      <c r="AK31" s="5"/>
+      <c r="AL31" s="5"/>
+      <c r="AM31" s="5"/>
+      <c r="AN31" s="5"/>
+      <c r="AO31" s="5"/>
+      <c r="AP31" s="5"/>
+      <c r="AQ31" s="5"/>
     </row>
     <row r="32" s="2" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H32" s="9"/>
+      <c r="A32" s="0"/>
+      <c r="B32" s="0"/>
+      <c r="C32" s="0"/>
+      <c r="D32" s="0"/>
+      <c r="E32" s="0"/>
+      <c r="F32" s="0"/>
+      <c r="G32" s="0"/>
+      <c r="H32" s="0"/>
     </row>
     <row r="33" s="2" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="A33" s="0"/>
+      <c r="B33" s="0"/>
+      <c r="C33" s="0"/>
+      <c r="D33" s="0"/>
+      <c r="E33" s="0"/>
+      <c r="F33" s="0"/>
+      <c r="G33" s="0"/>
+      <c r="H33" s="0"/>
     </row>
     <row r="34" s="2" customFormat="true" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
+      <c r="A34" s="0"/>
+      <c r="B34" s="0"/>
+      <c r="C34" s="0"/>
+      <c r="D34" s="0"/>
+      <c r="E34" s="0"/>
+      <c r="F34" s="0"/>
+      <c r="G34" s="0"/>
+      <c r="H34" s="0"/>
     </row>
     <row r="35" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="4"/>
-      <c r="AC35" s="4"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="4"/>
-      <c r="AF35" s="4"/>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="4"/>
-      <c r="AI35" s="4"/>
-      <c r="AJ35" s="4"/>
-      <c r="AK35" s="4"/>
-      <c r="AL35" s="4"/>
-      <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="4"/>
-      <c r="AP35" s="4"/>
-      <c r="AQ35" s="4"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5"/>
+      <c r="AA35" s="5"/>
+      <c r="AB35" s="5"/>
+      <c r="AC35" s="5"/>
+      <c r="AD35" s="5"/>
+      <c r="AE35" s="5"/>
+      <c r="AF35" s="5"/>
+      <c r="AG35" s="5"/>
+      <c r="AH35" s="5"/>
+      <c r="AI35" s="5"/>
+      <c r="AJ35" s="5"/>
+      <c r="AK35" s="5"/>
+      <c r="AL35" s="5"/>
+      <c r="AM35" s="5"/>
+      <c r="AN35" s="5"/>
+      <c r="AO35" s="5"/>
+      <c r="AP35" s="5"/>
+      <c r="AQ35" s="5"/>
     </row>
     <row r="36" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="4"/>
-      <c r="AC36" s="4"/>
-      <c r="AD36" s="4"/>
-      <c r="AE36" s="4"/>
-      <c r="AF36" s="4"/>
-      <c r="AG36" s="4"/>
-      <c r="AH36" s="4"/>
-      <c r="AI36" s="4"/>
-      <c r="AJ36" s="4"/>
-      <c r="AK36" s="4"/>
-      <c r="AL36" s="4"/>
-      <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="4"/>
-      <c r="AP36" s="4"/>
-      <c r="AQ36" s="4"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+      <c r="AA36" s="5"/>
+      <c r="AB36" s="5"/>
+      <c r="AC36" s="5"/>
+      <c r="AD36" s="5"/>
+      <c r="AE36" s="5"/>
+      <c r="AF36" s="5"/>
+      <c r="AG36" s="5"/>
+      <c r="AH36" s="5"/>
+      <c r="AI36" s="5"/>
+      <c r="AJ36" s="5"/>
+      <c r="AK36" s="5"/>
+      <c r="AL36" s="5"/>
+      <c r="AM36" s="5"/>
+      <c r="AN36" s="5"/>
+      <c r="AO36" s="5"/>
+      <c r="AP36" s="5"/>
+      <c r="AQ36" s="5"/>
     </row>
     <row r="37" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4"/>
-      <c r="AB37" s="4"/>
-      <c r="AC37" s="4"/>
-      <c r="AD37" s="4"/>
-      <c r="AE37" s="4"/>
-      <c r="AF37" s="4"/>
-      <c r="AG37" s="4"/>
-      <c r="AH37" s="4"/>
-      <c r="AI37" s="4"/>
-      <c r="AJ37" s="4"/>
-      <c r="AK37" s="4"/>
-      <c r="AL37" s="4"/>
-      <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="4"/>
-      <c r="AP37" s="4"/>
-      <c r="AQ37" s="4"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5"/>
+      <c r="AA37" s="5"/>
+      <c r="AB37" s="5"/>
+      <c r="AC37" s="5"/>
+      <c r="AD37" s="5"/>
+      <c r="AE37" s="5"/>
+      <c r="AF37" s="5"/>
+      <c r="AG37" s="5"/>
+      <c r="AH37" s="5"/>
+      <c r="AI37" s="5"/>
+      <c r="AJ37" s="5"/>
+      <c r="AK37" s="5"/>
+      <c r="AL37" s="5"/>
+      <c r="AM37" s="5"/>
+      <c r="AN37" s="5"/>
+      <c r="AO37" s="5"/>
+      <c r="AP37" s="5"/>
+      <c r="AQ37" s="5"/>
     </row>
     <row r="38" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
-      <c r="AF38" s="4"/>
-      <c r="AG38" s="4"/>
-      <c r="AH38" s="4"/>
-      <c r="AI38" s="4"/>
-      <c r="AJ38" s="4"/>
-      <c r="AK38" s="4"/>
-      <c r="AL38" s="4"/>
-      <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="4"/>
-      <c r="AP38" s="4"/>
-      <c r="AQ38" s="4"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
+      <c r="AA38" s="5"/>
+      <c r="AB38" s="5"/>
+      <c r="AC38" s="5"/>
+      <c r="AD38" s="5"/>
+      <c r="AE38" s="5"/>
+      <c r="AF38" s="5"/>
+      <c r="AG38" s="5"/>
+      <c r="AH38" s="5"/>
+      <c r="AI38" s="5"/>
+      <c r="AJ38" s="5"/>
+      <c r="AK38" s="5"/>
+      <c r="AL38" s="5"/>
+      <c r="AM38" s="5"/>
+      <c r="AN38" s="5"/>
+      <c r="AO38" s="5"/>
+      <c r="AP38" s="5"/>
+      <c r="AQ38" s="5"/>
     </row>
     <row r="39" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1384,11 +1552,56 @@
     <row r="70" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="71" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="72" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="73" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="74" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="75" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="76" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="77" s="2" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1445,10 +1658,10 @@
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A25:H25"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" display="https://apollofr76.github.io/Portfolio/"/>
+    <hyperlink ref="A5" r:id="rId1" display="Adresse URL du portfolio : https://apollofr76.github.io/Portfolio/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
